--- a/site/File-Collection-ServiceNow-Integration-Guide/headings.xlsx
+++ b/site/File-Collection-ServiceNow-Integration-Guide/headings.xlsx
@@ -605,12 +605,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KSPZNWYRMPGG3XBDQWA0T57K</t>
+          <t>h_01KSQ6D1ATZPVNB52Z70YW90Y1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/File-Collection-ServiceNow-Integration-Guide/#h_01KSPZNWYRMPGG3XBDQWA0T57K</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/File-Collection-ServiceNow-Integration-Guide/#h_01KSQ6D1ATZPVNB52Z70YW90Y1</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KSPZNWYR4TTXQK3069FPT8PX</t>
+          <t>h_01KSQ6D1AT45E3T9C3BQF3F7YK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/File-Collection-ServiceNow-Integration-Guide/#h_01KSPZNWYR4TTXQK3069FPT8PX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/File-Collection-ServiceNow-Integration-Guide/#h_01KSQ6D1AT45E3T9C3BQF3F7YK</t>
         </is>
       </c>
     </row>
